--- a/光伏配储项目/电价数据/2026/远丰站.xlsx
+++ b/光伏配储项目/电价数据/2026/远丰站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.79334</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.3846</v>
+      </c>
+      <c r="C117" t="n">
+        <v>1.06028</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.88683</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.59188</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.75649</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.81784</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.44225</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.45984</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.43205</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.42665</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.42494</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.41299</v>
+      </c>
+      <c r="N117" t="n">
+        <v>1.40058</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.40006</v>
+      </c>
+      <c r="P117" t="n">
+        <v>1.38788</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.40486</v>
+      </c>
+      <c r="R117" t="n">
+        <v>1.42819</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.41676</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.35569</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.39477</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.38792</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.42062</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.39517</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.42449</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.41752</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>1.42768</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.41525</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.44748</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.50227</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30002</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.40096</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30827</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.3117</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.32788</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.35113</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.37415</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.32278</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.35019</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.12753</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.14028</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.34968</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.14563</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.08025</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.11918</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.52275</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.21422</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.31192</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.28773</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.05162</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.89036</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>1.40146</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.14857</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.22074</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.23018</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.23541</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.2194</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>0.7865700000000001</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.30149</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.45207</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.15357</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.33956</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.35337</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.2905</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.29786</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.51464</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.6707799999999999</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.7611599999999999</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.81802</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.7307400000000001</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.48132</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.39441</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.43119</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.43636</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.65796</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>1.18023</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.7878999999999999</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.51705</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>1.3688</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>1.59712</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.7563300000000001</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.9995499999999999</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>1.05695</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.75267</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.8706699999999999</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.79627</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.75681</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.51739</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.47932</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.46863</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41564</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42526</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32887</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.70792</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.76835</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.87053</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.91496</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.49387</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.51415</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.50214</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.50237</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.48467</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.39913</v>
+      </c>
+      <c r="N118" t="n">
+        <v>1.46683</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.37789</v>
+      </c>
+      <c r="P118" t="n">
+        <v>1.37796</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>1.37714</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33619</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.36561</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.35105</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.351</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.36316</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.36689</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.35047</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.37309</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>1.40638</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.7088099999999999</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.8042899999999999</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.45456</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.43553</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.3771600000000001</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.34744</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.38688</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.42635</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.5087200000000001</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.35426</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.339</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.35663</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.33006</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.33232</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.39337</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.30304</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.33227</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.34155</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.37682</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.51062</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.78203</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0.99612</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.33541</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.52544</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.89181</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.8479099999999999</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.50048</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.73077</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>1.45331</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>1.0868</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>1.0273</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.29825</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.35085</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.37567</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.47182</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.54764</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.50087</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.5233300000000001</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.91728</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.62136</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.93675</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>1.29079</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>1.52345</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>1.17597</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>1.1042</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>1.56984</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>1.47215</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>1.62773</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>1.40631</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>1.45705</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>1.0139</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>1.3494</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.90146</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>1.42743</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>1.50613</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>1.34171</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>1.12727</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.44995</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.78872</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.80937</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.44879</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.42795</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.44341</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.33349</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.37553</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35462</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33458</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.5073</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.48641</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.48668</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.3776</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.44721</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.41386</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.36838</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.38906</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.38254</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.363</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.42736</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.44275</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33566</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.36992</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.39529</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.3667</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.36759</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35553</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.36099</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.35159</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.36269</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.35687</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.38311</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39483</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.47172</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.44372</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.43756</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.34725</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.39408</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35266</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.36725</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.34734</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.49776</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.6664</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.89637</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.81432</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.7556799999999999</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.24672</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.3901</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.37125</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.33104</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.37146</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.40264</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.41692</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.56086</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.50401</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.82397</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.40369</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.59809</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.72682</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.8151</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.5277200000000001</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.54884</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.79779</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>1.22789</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.68172</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.6002999999999999</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.49388</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.45431</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.42426</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.39407</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.78249</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.52116</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.50469</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.57055</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.59634</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.5450199999999999</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.5649999999999999</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>1.26268</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.6158400000000001</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>1.00531</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.49128</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.5328999999999999</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.5754400000000001</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.9550299999999999</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>1.01212</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>1.37731</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.8287899999999999</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.8170700000000001</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.6581699999999999</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.8986900000000001</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.6095700000000001</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.89212</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.56255</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>1.27649</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.85775</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.56062</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.48405</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.6176200000000001</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.5137</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.45651</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.39729</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.36204</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.34847</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34193</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31894</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.52119</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.49351</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.44419</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.38921</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.38916</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.35987</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.36697</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.35886</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.38742</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.38555</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.3614</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.44835</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.35984</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.34847</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.36297</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.35739</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.3585</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.3374</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.33493</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.33157</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.33406</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.33146</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.35005</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33886</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.35094</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.38506</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.38835</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.34857</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.37473</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.34395</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.39322</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.41589</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.5190900000000001</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.35649</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.73775</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.34049</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.62134</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.85703</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>1.17441</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.7799700000000001</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.8949</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>1.36849</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.6772100000000001</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>1.40216</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>1.24258</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>1.15351</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.97039</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>1.46895</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.94337</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.35111</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.3604</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.45307</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.6033200000000001</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.41778</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.3343</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.32056</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.3476</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.48045</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.40554</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.39863</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.90915</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.9142400000000001</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.80467</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>1.36864</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>1.40676</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.42648</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.49418</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.45026</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.46127</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.39951</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.47375</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.52055</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>1.00695</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.9030499999999999</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>1.40532</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.9673200000000001</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.8620800000000001</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.5007900000000001</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.7875700000000001</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.7393</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.635</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.41563</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.53612</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.53326</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.34631</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.34151</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.31904</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.32304</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.3204</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.31392</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31807</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.31972</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.31698</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.71948</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.84113</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.38237</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.36142</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.36344</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.32903</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.32801</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.33209</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.32072</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.31901</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.31607</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.31877</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.31852</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.31514</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.31643</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.31287</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.31426</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.31937</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.31604</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.31071</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.31008</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31338</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.31467</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32452</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.3326</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32612</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.32102</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.32228</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.31977</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.33196</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.44248</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.31198</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.28649</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.33005</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.32508</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.30925</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.31871</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.3038</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.30404</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.2015</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.40522</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.36566</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.22312</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.15371</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.28748</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>0.25052</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>0.34054</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.27156</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>0.19275</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>0.36336</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>0.34129</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>0.05926</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.38073</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.37814</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.22547</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.36574</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.21121</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.06484000000000001</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>0.08123999999999999</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>0.008400000000000001</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.00338</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>1.1394</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.2696</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.29758</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.29994</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.30811</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.31908</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.31367</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31546</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33545</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.33572</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33585</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.33336</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.37636</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.38209</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.37664</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.37093</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.35724</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.38824</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.39156</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.40019</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.46053</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.37052</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.38979</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.39136</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.48456</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.35213</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35661</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34432</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35379</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.34348</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.36587</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.5819500000000001</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.37798</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.40063</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.38425</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.37868</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.35144</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.34314</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.35076</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.3014</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.29993</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.28382</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.33197</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.27096</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.34055</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.33733</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.32838</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.28182</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.31189</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.30857</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.2936</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.29116</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.28949</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.32867</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.31893</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.33241</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.34537</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.31114</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.30518</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.1028</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04359</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04697999999999999</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.0441</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04476</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04398</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>0.35594</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.01508</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.21587</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.05408</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>0.28968</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.20476</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>0.07463</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04392</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04394</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.0456</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04561</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04369</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04335</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04549</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04339</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>0.23256</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.04529</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04525</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04538</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04358</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04422</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.06842000000000001</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.06665</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04471</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.04997</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04984</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.0474</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04790999999999999</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.19975</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14272</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.28994</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29465</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30454</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.29982</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29492</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29282</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29329</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29225</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29678</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29074</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29497</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.26875</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29381</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30855</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30375</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30221</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31434</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31839</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.34723</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.34774</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.34126</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.36181</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.36112</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.33222</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.32569</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.31388</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31032</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.39712</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.34612</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32042</v>
+      </c>
+      <c r="H123" t="n">
+        <v>1.19204</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31463</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30134</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28114</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29442</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29069</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28802</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27116</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27089</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17236</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.1586</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17092</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.1477</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15943</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15858</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23612</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.214</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22651</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26883</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28566</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29075</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.31932</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.28069</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28043</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.2707</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28091</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32236</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30493</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.9157799999999999</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>1.10263</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.89625</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.29731</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>1.38626</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.37954</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.42769</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.45556</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33182</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41844</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41528</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.38718</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.40242</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30005</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30095</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29929</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.29998</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15654</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.2943</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31093</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31343</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31269</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32184</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34628</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30067</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33083</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38545</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.5076700000000001</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79098</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.6220399999999999</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78525</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49797</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.7810199999999999</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92039</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49456</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.9142100000000001</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.86288</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.29621</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.35365</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.8875</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.6316000000000001</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.18709</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.87388</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.9017500000000001</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.33085</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.03291</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.53079</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.79099</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.60821</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.77298</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.77754</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.8767699999999999</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87387</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49315</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.39868</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.41983</v>
+      </c>
+      <c r="D124" t="n">
+        <v>1.03951</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.47694</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87883</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55102</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.62185</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.53832</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.49769</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.94928</v>
+      </c>
+      <c r="L124" t="n">
+        <v>1.00008</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.9997200000000001</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.44969</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.38817</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45268</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.41969</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.34798</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.39877</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.36326</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.38381</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.41027</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.42793</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.34055</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.3876</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.3468</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.33649</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.32994</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.3412</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.38846</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.34745</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.44958</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.3482</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.39415</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.38724</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.5642999999999999</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.41604</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.5867899999999999</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.71347</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.87727</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.46692</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>1.16102</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.86413</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.88744</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.5817899999999999</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>1.33499</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.8922899999999999</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.88186</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.6423099999999999</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.89919</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>1.30344</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>1.42972</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.64078</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.59178</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.71915</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.31055</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.35307</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.33049</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.32079</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.40648</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.33451</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.3172</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.31954</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31908</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.31956</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.33664</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.31699</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.30953</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.31899</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.30173</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.29587</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.31141</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.31016</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.31087</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.29004</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.30128</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.30525</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.31386</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.31188</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.31655</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.34878</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.33156</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.33472</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.33261</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.32491</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.32936</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.3276</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.39016</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.39236</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.42593</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.39433</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.37566</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.35936</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.34793</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32835</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.91432</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.35074</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.44597</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.40794</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.39515</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.43999</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.36804</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.39191</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.35304</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.35624</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.3416</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.34075</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.33633</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.32507</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.34944</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.33743</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.37975</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.46546</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.34726</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.37088</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.33496</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.34102</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.34454</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.35713</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.34717</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.35138</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.30836</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.30968</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.32595</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.33055</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.33199</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.34187</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.31285</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.31114</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.28836</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.31267</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.3095</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.30052</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.1873</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.30428</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.30812</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.34018</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.33383</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.35657</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.31042</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.27306</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.19784</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.30532</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.29878</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.32045</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.28155</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.3093399999999999</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.30978</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.34855</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.357</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.3092200000000001</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.30285</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.31134</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.31304</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.3188</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.31029</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.29889</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.296</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.30136</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.30943</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.3077</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.28864</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.33834</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.25386</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.33908</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.31354</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.32754</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.32946</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.27456</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.33771</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.32149</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.33035</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.30259</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.33926</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.32935</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.37075</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.34133</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.41521</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.88607</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.33377</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.42042</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.34528</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.44102</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.32824</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.40229</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35224</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.38225</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.3801</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.53955</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.32385</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.86851</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.44313</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.14083</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.68768</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.77803</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.63939</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.5126900000000001</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.40566</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.44108</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.49106</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.4313</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.41834</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.40613</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.40536</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.40626</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.46637</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.40557</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.42618</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.39148</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.42675</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.38473</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.40251</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.42086</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.38908</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.41686</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.40808</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.4056</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.40775</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.37994</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.39693</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.3913</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.38121</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.4874</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.35751</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.3113</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.28855</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.34686</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.3574</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.30611</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.33484</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.30466</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.30877</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.29962</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.5266799999999999</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.35754</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.23525</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.24844</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.3022</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.1547</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.27454</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.27531</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>-0.01185</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.33558</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.30113</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.26002</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.25314</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.30968</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.28182</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.29787</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.31348</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.28941</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.30505</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.31094</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.3192</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.31981</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.31147</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.32961</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.331</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.3891</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.38579</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.34463</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.35338</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.33363</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.32296</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.36071</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.33552</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.3464</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.35566</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.35517</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.3420899999999999</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.54525</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.4358</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.79244</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.43715</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>1.03889</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.36557</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.44182</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.37114</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.35731</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.32552</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.32562</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.32099</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.30899</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.3928</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.32163</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.32442</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.30433</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.32924</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.29834</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.30225</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.29706</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.29808</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.29034</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.29344</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.31144</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.30983</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.31193</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.30801</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.2857</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.28577</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.30135</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.31618</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.30349</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.25106</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.29045</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.3515</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.2522</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.31843</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.35707</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.32956</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.32897</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.32941</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.32571</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.31681</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.29394</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.3114</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>1.23699</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.32176</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.2721</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.26205</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.30952</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.35095</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.22973</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.23902</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.31818</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.32288</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.35145</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.23367</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.2653</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.31321</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.31983</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.28362</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.29143</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.30127</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.30303</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.29595</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.24078</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.28827</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.33083</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.24809</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.29298</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.26585</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.32183</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.31124</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.44501</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.34796</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.39976</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.31833</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.36306</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.35382</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.42111</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.3335</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.3626</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.33687</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.378</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.3452</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.36426</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.41471</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.37584</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.36966</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.37709</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.37486</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.41895</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.40662</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.40715</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.41154</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.43743</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.39398</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.38213</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.38987</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.38378</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.34237</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.34332</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.32545</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.33359</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.3279</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.48792</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.38207</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.43319</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.39779</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.39122</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.35425</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.36317</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.36204</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.3732</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.37291</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.36344</v>
+      </c>
+      <c r="N128" t="n">
+        <v>1.36449</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.3479</v>
+      </c>
+      <c r="P128" t="n">
+        <v>1.37265</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>1.35559</v>
+      </c>
+      <c r="R128" t="n">
+        <v>1.36205</v>
+      </c>
+      <c r="S128" t="n">
+        <v>1.33812</v>
+      </c>
+      <c r="T128" t="n">
+        <v>1.33574</v>
+      </c>
+      <c r="U128" t="n">
+        <v>1.34277</v>
+      </c>
+      <c r="V128" t="n">
+        <v>1.33378</v>
+      </c>
+      <c r="W128" t="n">
+        <v>1.32992</v>
+      </c>
+      <c r="X128" t="n">
+        <v>1.33416</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>1.32991</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>1.3391</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>1.41714</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.35373</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.36274</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.34681</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.3315</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.3294</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.3317</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.32056</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.33294</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>1.33978</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.35437</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.29438</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.31585</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.32641</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.32048</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.30081</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.31407</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.3023</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.93332</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.8304600000000001</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>1.36017</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>1.39593</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.25315</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.2785</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.30088</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.30131</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31806</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.3178</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.31722</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>1.35959</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>1.31353</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>1.32435</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>1.29779</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.23949</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.31271</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.30305</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.32006</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.51305</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.5277999999999999</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.41988</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.5781499999999999</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.5319700000000001</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>1.41647</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.33373</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.81652</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.88875</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.37427</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.40708</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.34145</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.4059700000000001</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>1.7454</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.37787</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>1.37156</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>1.42682</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.42551</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.42019</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>1.70351</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.34065</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.34341</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>1.47265</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.35838</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.41762</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.35964</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>1.36476</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.36867</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.33981</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.3479100000000001</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.33539</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.35291</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.45789</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.36384</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.47062</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.36486</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.34169</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.35156</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.34485</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.33698</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.33067</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.33546</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.33478</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.33822</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.33993</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.33707</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.33247</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.33154</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.33613</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.33159</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.32805</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.33292</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.32863</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.33022</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.33308</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.33778</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.36002</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.3732799999999999</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.36721</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.36099</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.40823</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.33157</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.71084</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.8226599999999999</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.8059400000000001</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>1.49537</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.72711</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>1.45364</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>1.13053</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.8090900000000001</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.79273</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>1.09683</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.76334</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>1.16206</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>1.19758</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.7137100000000001</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>1.12214</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.39324</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>1.3097</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.61045</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>1.47379</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>1.27726</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>1.50556</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>1.64578</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>1.26494</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>1.56504</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.99942</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.74934</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>1.33682</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.75652</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.7238600000000001</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.81191</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.7403200000000001</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.7348600000000001</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>1.28348</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.86124</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>1.67693</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.84077</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.82267</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>1.09773</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.77024</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.6501399999999999</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.60487</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.51507</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.36772</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>1.50295</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.23996</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.36886</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.3515</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.32904</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.3376</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.33424</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.31248</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.33814</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.57889</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.3083399999999999</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.32002</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.48554</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.39616</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.41257</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.3365</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.32165</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.33365</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.35049</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.31211</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.39381</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.36361</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.32842</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.32357</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.32305</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.31706</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.31458</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.37921</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.32611</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.29823</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.28651</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.30082</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.31295</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.31612</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.31151</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.29796</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.30281</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.31376</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.31613</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.30795</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.29397</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.31841</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.30901</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.32949</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.34879</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.37235</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.37087</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.32743</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>1.0644</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.3627</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.34167</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.48598</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.34221</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.33078</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.31496</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.33277</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.33258</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.30931</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.32561</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.27638</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.32424</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.33827</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.31225</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.31829</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.3206</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.32723</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.33357</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.32936</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.31658</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.30588</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.3092200000000001</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.31081</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.84941</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.33664</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>1.19553</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>1.45884</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>1.11111</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.52242</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.33037</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.35603</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.36847</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.34153</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.33903</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.33839</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.86212</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.37851</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.85919</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.33832</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.35147</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.35737</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.34928</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.34145</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.35046</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.34845</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.35318</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.35969</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.36335</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.36447</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.36131</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.34764</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.35628</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.35798</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.32404</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.30606</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.34307</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.3227</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.34267</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.32866</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.34345</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.34245</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.34346</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.34442</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.34389</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.3431</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.33352</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.34246</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.33931</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.27255</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.3400899999999999</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.33431</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.33463</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.32234</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.33264</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.3331</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.32708</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.34931</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.31744</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.32548</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.33272</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.3342</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.32475</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.32418</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.3381</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.32389</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.33561</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.3355</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.32934</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.32628</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.31575</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.3336</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.32942</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.31837</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.32457</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.29984</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.32169</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.32426</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.32295</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.31442</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.32329</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.31471</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.3156600000000001</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.32349</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.32076</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.32861</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31755</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.3697</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.33759</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.31922</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.74564</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>1.31131</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.42012</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.54695</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.42459</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.38768</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.41563</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.4958</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.3411</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.36439</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.33329</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.3503</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.58805</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.38494</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.3468</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.35268</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.41775</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.34451</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.38563</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.44309</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.34876</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.35182</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.40535</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.34177</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.3696</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.49713</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.422</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.37068</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.40401</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.6184700000000001</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.37399</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.36886</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.6503099999999999</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.42638</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.66788</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.61029</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.89102</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.34343</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.7150299999999999</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.3523</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.33272</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.33345</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.32207</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.40413</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.36927</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.35967</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.35503</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.35217</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.35184</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.3511</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.34975</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.35196</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.34582</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.35297</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.34908</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.34911</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.34506</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.34805</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.35246</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.35279</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.34066</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.35046</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.35176</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.3495</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.35306</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.35306</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.3626</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.35886</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.37287</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.34955</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.34946</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.34417</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.34486</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.3509</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.34245</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.3249</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>1.40029</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.47174</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.84517</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.5653899999999999</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.9005299999999999</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.46654</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.66343</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.3407</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.33545</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>1.21011</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>1.23369</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>1.27124</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.96958</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.89873</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.90042</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.89973</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.8998999999999999</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.8994800000000001</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.8998200000000001</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.89927</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.9284600000000001</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.891</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.90038</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.89818</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.899</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.34121</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.73436</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.56241</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.88739</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.76225</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>1.3028</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.7132200000000001</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.69075</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.34759</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.94938</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.72009</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.94002</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.36238</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>1.36613</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>1.34528</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>1.37913</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>1.02211</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.9799099999999999</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>1.38129</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.88215</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>1.08926</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.8943099999999999</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.8666200000000001</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.7778999999999999</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>1.41683</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.74549</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.40506</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.39615</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.36547</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.36811</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.3559</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.34981</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34576</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.45228</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.52371</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.47144</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.61117</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.39428</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.39439</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.38344</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.38815</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.38775</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.39373</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.38059</v>
+      </c>
+      <c r="N133" t="n">
+        <v>1.38764</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.93652</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.94074</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.90562</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.96094</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.8936799999999999</v>
+      </c>
+      <c r="T133" t="n">
+        <v>1.31969</v>
+      </c>
+      <c r="U133" t="n">
+        <v>1.02606</v>
+      </c>
+      <c r="V133" t="n">
+        <v>1.01153</v>
+      </c>
+      <c r="W133" t="n">
+        <v>1.00786</v>
+      </c>
+      <c r="X133" t="n">
+        <v>1.01158</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>1.02894</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.90439</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.94037</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.41382</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.49899</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.45615</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.41839</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.45337</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.41696</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.5905499999999999</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>1.28374</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.9369400000000001</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>1.331</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>1.36764</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>1.77579</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>1.44728</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.42752</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.36407</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.348</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.35588</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.51154</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.5135599999999999</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.53622</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>1.36339</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>1.48949</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.42708</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.4584</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>1.13002</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>1.29554</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>1.77796</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>1.50232</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>1.50667</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>1.49266</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>1.49244</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>1.7218</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>1.33929</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>1.31543</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.33429</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.34942</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.3376</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.35656</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.35163</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.35419</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.35941</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.37017</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.34472</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.36317</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.33165</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.39129</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.4108</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.45505</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.41781</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.46843</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.46856</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.50075</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.61505</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.7200700000000001</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.80921</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.58182</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.70329</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>1.56139</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.71335</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.72327</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.7646499999999999</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.61737</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.66561</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>1.24161</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.58243</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.44503</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.44157</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.43476</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.39559</v>
+      </c>
+      <c r="C134" t="n">
+        <v>1.10136</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.97338</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.41427</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.42447</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.42755</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.41746</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.41601</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.4092</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.37965</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.41256</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.3726</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.971</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.97766</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.9790099999999999</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.98317</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.9824299999999999</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.35324</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.35902</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.28981</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.34933</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.34268</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.35291</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.99324</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.9741599999999999</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.36567</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.37259</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.34918</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.35444</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.34821</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.37254</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.39495</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.35813</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.9929199999999999</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.39236</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.37846</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.37967</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.3514</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.35941</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.3393</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.33421</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.34145</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.99415</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>1.31468</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.508</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.478</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.47539</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.49575</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.48485</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.64808</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.49681</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.5745800000000001</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.53342</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.58412</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.97563</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.3438</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.1585</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.22124</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.30288</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.29956</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.32204</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.34358</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.3358</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.33804</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.33875</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.35677</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.37794</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.37777</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.50507</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.43051</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.3347</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.42394</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.41053</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.42258</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.40117</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.39147</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.34715</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.35037</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.36902</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.3775</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.32492</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.33716</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.36869</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.96813</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.99322</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.97946</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.3548</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.37364</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.33455</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.35631</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.31403</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.34774</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.33444</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.32897</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.29653</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.45613</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.71661</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.37205</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.35591</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.64979</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.34251</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.30837</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.29126</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.33458</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.27527</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.27276</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.95912</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.91231</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.31274</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.34451</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.30739</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.2607</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.29127</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.29898</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.3072</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.29486</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.29933</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.30381</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.25323</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.30829</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.25231</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.24659</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.32623</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.28673</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.27917</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.30725</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.24168</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.34284</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.30816</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.30686</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.302</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.18499</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.28223</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.24713</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.27164</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.26348</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.25957</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.09415000000000001</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.31701</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.30806</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.27001</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.25801</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.03353</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.28936</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.28186</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.19751</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.26328</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.31095</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.31273</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.30742</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.25094</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.26999</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.25795</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.24108</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.27629</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.28494</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.2745</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.32178</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.32353</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.31647</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.33905</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.33633</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.34568</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.36208</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.34123</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.35373</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.34546</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.37968</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.37686</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.42237</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.3023</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.35018</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.33852</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.35283</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.33175</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.33918</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.35798</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.3331</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.40772</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.36323</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.39447</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.33342</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.33751</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.32367</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.33468</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.32642</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.30531</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.33105</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.32131</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.30014</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.52239</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.32692</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.32673</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.32952</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.3269</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.26685</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.29154</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.28712</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.30583</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.23515</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.28496</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.29279</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.28874</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.24573</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.23424</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.23728</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.23727</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.23409</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.23409</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.236</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.2805</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.23045</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.23409</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.2344</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.27964</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.23439</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.23418</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.3263</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.24141</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.16074</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.26636</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.20763</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.01224</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.00043</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>-0.00021</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04957</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.14557</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.02129</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.03957</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.04959</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.01541</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.04286</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.04075</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.04859</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.04824000000000001</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02446</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.02924</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.04997</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.04959</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.0494</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0.00013</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.27445</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04964</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.0493</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.03826</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.01912</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.04958</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04963</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.03616</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.20137</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.26481</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.28828</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.2790899999999999</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.30386</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.30781</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.23859</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.31032</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.32801</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.34332</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.33629</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.33969</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.3096</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.31454</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.34913</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.33794</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.34207</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.33987</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.33809</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.34344</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.3376</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.36423</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.41751</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.35243</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.36629</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.34782</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.34337</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.34267</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.33486</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.3450299999999999</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.31329</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.32991</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29801</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.72422</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.62409</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.38427</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.41656</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.39065</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.41183</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.42011</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.35849</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.27908</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.33858</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.30607</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.29928</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.29474</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.24708</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.29844</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.2839100000000001</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.2414</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.23418</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.26898</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.25881</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.28789</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.25421</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.27973</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.2915</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.31402</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.43613</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.35453</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.33972</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.34571</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.25913</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.36457</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0.6569199999999999</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.82299</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.87648</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.85129</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.32586</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.38161</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.08809</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.1925</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.27504</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.29037</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.2987</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.30082</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.26413</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.29603</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.34242</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>-0.0466</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.25505</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.26784</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>-0.02649</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.27193</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>-0.01128</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.31074</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.31092</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.29322</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.05014</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.28522</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.29628</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.28819</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.30033</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.25058</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.28908</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.47136</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.30456</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.31983</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.33109</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.36059</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.37237</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.32983</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.35398</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.3442</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.37399</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>1.44143</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.7677200000000001</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.70184</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.7269</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>1.29236</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.9475399999999999</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.73399</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.8121799999999999</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.7824</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.83975</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.8379500000000001</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.8422500000000001</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.93949</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.74149</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.7783600000000001</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.74479</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.3735</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.35463</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.37159</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.36224</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.36208</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33007</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.46262</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.60233</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.63375</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.5646</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.493</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.45719</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.39926</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.38886</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.3802</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.36993</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.35228</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.33084</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.33505</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.32445</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.31676</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.46916</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.31842</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.31239</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.31236</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.30326</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.30765</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.27449</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.3389</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.33682</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.36269</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.4577</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.46799</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.3636</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.38067</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.32129</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.32177</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.33065</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.42149</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.37375</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.44233</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.32994</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.3959</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.37195</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.3094</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.3357</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.32375</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.34776</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.32781</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.3014</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.32296</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.31737</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.29905</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.2471</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.30172</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.29284</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.29142</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.32619</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.31025</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.30786</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.31365</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.30685</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.32704</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.31446</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.31545</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.32122</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.33323</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.33672</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.31917</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.31606</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.31147</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.32798</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.29248</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.27458</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.28433</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.27517</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.30019</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.31747</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.3425299999999999</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.38293</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.36904</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.35439</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.33052</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.3544</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.29854</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.35769</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.40715</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.60497</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.32711</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.5116700000000001</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.41349</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.30348</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.39729</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.40043</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.38222</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.45639</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.34896</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.35172</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.33508</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.33611</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.33306</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.41461</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.41671</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.40225</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.38502</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.37839</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.37443</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.37208</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.35357</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.35558</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.3483</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.34801</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.49964</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.34512</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.34287</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.33947</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.34844</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.33292</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.33222</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.3261</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.32818</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.32972</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.3298</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.33958</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.33217</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>1.15337</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.3405</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.34808</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.34181</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.3511</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.39557</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.36096</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.35198</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.5301399999999999</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.74591</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.49956</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.4273</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.498</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.41664</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.28742</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.29998</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.31371</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.3299</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.3377</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.36495</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.33544</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.36822</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.33244</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.28757</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.40073</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.37944</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.39505</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.38976</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.36011</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.32501</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.39964</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.31064</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.37839</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.32236</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.31379</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.31828</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.30761</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.32817</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.32828</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.80926</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.5361900000000001</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.44469</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>1.76444</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.93628</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.66779</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.8859</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.65723</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.99315</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.7880900000000001</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.6601</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.50517</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.44543</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.44323</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.56916</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.62605</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.7186699999999999</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.43664</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.4116</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.35056</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.41186</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.37366</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.35325</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.37557</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.35992</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.23147</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.35232</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.34037</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.34869</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.33589</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.44838</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.3771600000000001</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.37241</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.36514</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.36093</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.34351</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.35235</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.36337</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.35692</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.35536</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.35125</v>
+      </c>
+      <c r="N140" t="n">
+        <v>1.34791</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.34466</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.34233</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.34365</v>
+      </c>
+      <c r="R140" t="n">
+        <v>1.34327</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.33624</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.31741</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.33636</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.33087</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.32881</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.3268</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.33858</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.33494</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.34505</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.36478</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.34749</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.35437</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.34174</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.34895</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.34743</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.3456</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>1.37871</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>1.39122</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.36322</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.35387</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.43493</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.37993</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.36028</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.37248</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.35321</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.31054</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.8606200000000001</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>1.03271</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.87702</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>1.09002</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.39284</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.2926</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.51585</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.41187</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.3739</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.44628</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.31622</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.33662</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.79872</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.32531</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.33352</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.34171</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.3382</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.32487</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.34421</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.34287</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.36584</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.36324</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.36988</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.42994</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.37347</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.39266</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.37188</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.37254</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.41623</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.4097</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.5102</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.73749</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.6902699999999999</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>1.45266</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.63446</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.92248</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.6131</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.47009</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>1.07952</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.8829199999999999</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>1.70964</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>1.51759</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.77415</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.58125</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.59474</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.40844</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.35607</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.3598</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.34916</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.35311</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.29923</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.35482</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.35739</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.34462</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.34754</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.338</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.32288</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.3343</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.32781</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.32954</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.34112</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.31987</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.36107</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.34092</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.33043</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.33606</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.33331</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.20339</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.32175</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.32409</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.33624</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.3235</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.33139</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.34432</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.33923</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.33272</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.37355</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.3736</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.35124</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.33698</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.33461</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.33617</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.35786</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.33383</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.34648</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.3495</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.3348</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.34401</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.40716</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>1.02967</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.7715700000000001</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.44917</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.62219</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.8059400000000001</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.48481</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>1.03997</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.81221</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.31747</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>1.53419</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.4536</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.42318</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.82792</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.5460199999999999</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>1.19495</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.76017</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>1.05633</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.44927</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.75299</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.8553999999999999</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.7514400000000001</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.4702</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.3483</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.34028</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.40223</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.39482</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.35972</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.41495</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.79149</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.69459</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.40218</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.36402</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.3699</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.51415</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.8690399999999999</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.46203</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.5307000000000001</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>1.13906</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.5581799999999999</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.80801</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.45126</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.5915900000000001</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>1.16182</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.53967</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.58116</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.54389</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.75536</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.39589</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.4142</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.40085</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.36685</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.37999</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.44419</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.34519</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.35953</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.3427</v>
+      </c>
+      <c r="C142" t="n">
+        <v>1.07111</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.67911</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.5505800000000001</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.56568</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.74312</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.36375</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.43428</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.3701</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.37909</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.36803</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.3664</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.36982</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.36584</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.36208</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.36554</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.36573</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.36485</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.36546</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.36091</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.35538</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.3561</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.35983</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.3575</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.35654</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.3470299999999999</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.35625</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.35096</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.36888</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.35613</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.34367</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.34563</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.35036</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.35774</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.35978</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.35454</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.34164</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.3736</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.36405</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.35531</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.36236</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.59663</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.39661</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>1.19237</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>1.34777</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>1.43638</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>1.32296</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.34111</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>1.04508</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.9024</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.78828</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.8036799999999999</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.90915</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.84851</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>1.75151</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>1.61927</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>1.33262</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>1.323</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.79557</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>1.35003</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.7934500000000001</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.8171</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.358</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.32934</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.3537</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.3449</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.34807</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.37247</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.42475</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.42552</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.40188</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.38184</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.35373</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.36116</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.38099</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.42029</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.43178</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.52324</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.48561</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.4584</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.42279</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.38162</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.41599</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.39101</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.79901</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.81287</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.4739</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>1.575</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.64274</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.60025</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.42678</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.35476</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.35502</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.3559</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.35649</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.34823</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.41039</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.38325</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.36058</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.37153</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.3744</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.37273</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.3647</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.36652</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.3603</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.36524</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.35633</v>
+      </c>
+      <c r="N143" t="n">
+        <v>1.16331</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.36085</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.34973</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.3644</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.35114</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.35564</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.35384</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.35489</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.35101</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.35126</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.35368</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.35239</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.35492</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.34617</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.34139</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.35266</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.3472</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.34747</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.31192</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.31745</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.31697</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.17561</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.30595</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.29467</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.31073</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.14529</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.19797</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.14212</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.29076</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.04481</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.12141</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.33018</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.22597</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.2653</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.15043</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.14392</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.28834</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.19527</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.30418</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.2261</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.26146</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.15256</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.35637</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.3077</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.15286</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.31119</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.29989</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.19636</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.14198</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.27894</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.3599</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.32219</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.32119</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.38148</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.29568</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.33331</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.34644</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.33686</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.38958</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.39613</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.40782</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.38394</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.7505599999999999</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.57117</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.45032</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.95114</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.3424</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.39861</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.35865</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.4674700000000001</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.42552</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.37983</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.38617</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.42209</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.38304</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.48306</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.39462</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.46766</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.42758</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.43155</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.445</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.38162</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.38135</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.38261</v>
       </c>
     </row>
   </sheetData>
